--- a/e2e/expectedData/rekap_bayar_Bukti_Transfer_2026-01.xlsx
+++ b/e2e/expectedData/rekap_bayar_Bukti_Transfer_2026-01.xlsx
@@ -74,7 +74,7 @@
     <t>Notes : biaya transfer dipotong dari gaji karyawan</t>
   </si>
   <si>
-    <t>DILI, 26 August 2026</t>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>

--- a/e2e/expectedData/rekap_bayar_Bukti_Transfer_2026-01.xlsx
+++ b/e2e/expectedData/rekap_bayar_Bukti_Transfer_2026-01.xlsx
@@ -74,7 +74,7 @@
     <t>Notes : biaya transfer dipotong dari gaji karyawan</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
